--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128260976</v>
+        <v>128259345</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>92676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546464</v>
+        <v>546505</v>
       </c>
       <c r="R2" t="n">
-        <v>6690810</v>
+        <v>6690671</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,45 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128259345</v>
+        <v>128258306</v>
       </c>
       <c r="B3" t="n">
-        <v>92676</v>
+        <v>92631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546505</v>
+        <v>546466</v>
       </c>
       <c r="R3" t="n">
-        <v>6690671</v>
+        <v>6690978</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128258306</v>
+        <v>128260976</v>
       </c>
       <c r="B4" t="n">
-        <v>92631</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,43 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>150</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546466</v>
+        <v>546464</v>
       </c>
       <c r="R4" t="n">
-        <v>6690978</v>
+        <v>6690810</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -2527,45 +2527,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128257989</v>
+        <v>128259676</v>
       </c>
       <c r="B21" t="n">
-        <v>92676</v>
+        <v>91806</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546378</v>
+        <v>546564</v>
       </c>
       <c r="R21" t="n">
-        <v>6691073</v>
+        <v>6690571</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2598,11 +2598,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2629,45 +2624,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128259676</v>
+        <v>128257989</v>
       </c>
       <c r="B22" t="n">
-        <v>91806</v>
+        <v>92676</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546564</v>
+        <v>546378</v>
       </c>
       <c r="R22" t="n">
-        <v>6690571</v>
+        <v>6691073</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2700,6 +2695,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128259345</v>
+        <v>128258306</v>
       </c>
       <c r="B2" t="n">
-        <v>92676</v>
+        <v>92631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546505</v>
+        <v>546466</v>
       </c>
       <c r="R2" t="n">
-        <v>6690671</v>
+        <v>6690978</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,54 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128258306</v>
+        <v>128259345</v>
       </c>
       <c r="B3" t="n">
-        <v>92631</v>
+        <v>92676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546466</v>
+        <v>546505</v>
       </c>
       <c r="R3" t="n">
-        <v>6690978</v>
+        <v>6690671</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128258198</v>
+        <v>128260994</v>
       </c>
       <c r="B13" t="n">
-        <v>92049</v>
+        <v>92644</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>788</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546459</v>
+        <v>546356</v>
       </c>
       <c r="R13" t="n">
-        <v>6690988</v>
+        <v>6691087</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128260994</v>
+        <v>128258198</v>
       </c>
       <c r="B14" t="n">
-        <v>92644</v>
+        <v>92049</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>788</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546356</v>
+        <v>546459</v>
       </c>
       <c r="R14" t="n">
-        <v>6691087</v>
+        <v>6690988</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2527,45 +2527,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128259676</v>
+        <v>128257989</v>
       </c>
       <c r="B21" t="n">
-        <v>91806</v>
+        <v>92676</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546564</v>
+        <v>546378</v>
       </c>
       <c r="R21" t="n">
-        <v>6690571</v>
+        <v>6691073</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2598,6 +2598,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2624,45 +2629,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128257989</v>
+        <v>128259676</v>
       </c>
       <c r="B22" t="n">
-        <v>92676</v>
+        <v>91806</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546378</v>
+        <v>546564</v>
       </c>
       <c r="R22" t="n">
-        <v>6691073</v>
+        <v>6690571</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2695,11 +2700,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -1460,45 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128259655</v>
+        <v>128260598</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>92287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Pundberget, Pundberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546552</v>
+        <v>546520</v>
       </c>
       <c r="R10" t="n">
-        <v>6690578</v>
+        <v>6690564</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1557,45 +1557,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128260598</v>
+        <v>128259655</v>
       </c>
       <c r="B11" t="n">
-        <v>92287</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pundberget, Pundberget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546520</v>
+        <v>546552</v>
       </c>
       <c r="R11" t="n">
-        <v>6690564</v>
+        <v>6690578</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -1460,45 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128260598</v>
+        <v>128259655</v>
       </c>
       <c r="B10" t="n">
-        <v>92287</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pundberget, Pundberget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546520</v>
+        <v>546552</v>
       </c>
       <c r="R10" t="n">
-        <v>6690564</v>
+        <v>6690578</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1557,45 +1557,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128259655</v>
+        <v>128260598</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>92287</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Pundberget, Pundberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546552</v>
+        <v>546520</v>
       </c>
       <c r="R11" t="n">
-        <v>6690578</v>
+        <v>6690564</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128260994</v>
+        <v>128258198</v>
       </c>
       <c r="B13" t="n">
-        <v>92644</v>
+        <v>92049</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>788</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546356</v>
+        <v>546459</v>
       </c>
       <c r="R13" t="n">
-        <v>6691087</v>
+        <v>6690988</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128258198</v>
+        <v>128260994</v>
       </c>
       <c r="B14" t="n">
-        <v>92049</v>
+        <v>92644</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>788</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546459</v>
+        <v>546356</v>
       </c>
       <c r="R14" t="n">
-        <v>6690988</v>
+        <v>6691087</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128258198</v>
+        <v>128260994</v>
       </c>
       <c r="B13" t="n">
-        <v>92049</v>
+        <v>92644</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>788</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546459</v>
+        <v>546356</v>
       </c>
       <c r="R13" t="n">
-        <v>6690988</v>
+        <v>6691087</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128260994</v>
+        <v>128258198</v>
       </c>
       <c r="B14" t="n">
-        <v>92644</v>
+        <v>92049</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>788</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546356</v>
+        <v>546459</v>
       </c>
       <c r="R14" t="n">
-        <v>6691087</v>
+        <v>6690988</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128258306</v>
+        <v>128260976</v>
       </c>
       <c r="B2" t="n">
-        <v>92631</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>150</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546466</v>
+        <v>546464</v>
       </c>
       <c r="R2" t="n">
-        <v>6690978</v>
+        <v>6690810</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,45 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128259345</v>
+        <v>128258306</v>
       </c>
       <c r="B3" t="n">
-        <v>92676</v>
+        <v>92639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546505</v>
+        <v>546466</v>
       </c>
       <c r="R3" t="n">
-        <v>6690671</v>
+        <v>6690978</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -878,45 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128260976</v>
+        <v>128259345</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>92684</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546464</v>
+        <v>546505</v>
       </c>
       <c r="R4" t="n">
-        <v>6690810</v>
+        <v>6690671</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +978,7 @@
         <v>128258256</v>
       </c>
       <c r="B5" t="n">
-        <v>92287</v>
+        <v>92295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128260190</v>
       </c>
       <c r="B6" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128258240</v>
       </c>
       <c r="B7" t="n">
-        <v>92676</v>
+        <v>92684</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128258585</v>
       </c>
       <c r="B8" t="n">
-        <v>92660</v>
+        <v>92668</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128259599</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,45 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128259655</v>
+        <v>128260598</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>92295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Pundberget, Pundberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546552</v>
+        <v>546520</v>
       </c>
       <c r="R10" t="n">
-        <v>6690578</v>
+        <v>6690564</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1557,45 +1557,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128260598</v>
+        <v>128259655</v>
       </c>
       <c r="B11" t="n">
-        <v>92287</v>
+        <v>98478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pundberget, Pundberget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546520</v>
+        <v>546552</v>
       </c>
       <c r="R11" t="n">
-        <v>6690564</v>
+        <v>6690578</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1657,7 +1657,7 @@
         <v>128258089</v>
       </c>
       <c r="B12" t="n">
-        <v>92660</v>
+        <v>92668</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128258198</v>
       </c>
       <c r="B13" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>128260994</v>
       </c>
       <c r="B14" t="n">
-        <v>92644</v>
+        <v>92652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>128259095</v>
       </c>
       <c r="B15" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>128258763</v>
       </c>
       <c r="B16" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>128259373</v>
       </c>
       <c r="B17" t="n">
-        <v>88611</v>
+        <v>88617</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>128259683</v>
       </c>
       <c r="B18" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>128259428</v>
       </c>
       <c r="B19" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128257918</v>
       </c>
       <c r="B20" t="n">
-        <v>92287</v>
+        <v>92295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,45 +2527,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128257989</v>
+        <v>128259676</v>
       </c>
       <c r="B21" t="n">
-        <v>92676</v>
+        <v>91814</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546378</v>
+        <v>546564</v>
       </c>
       <c r="R21" t="n">
-        <v>6691073</v>
+        <v>6690571</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2598,11 +2598,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2629,45 +2624,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128259676</v>
+        <v>128257989</v>
       </c>
       <c r="B22" t="n">
-        <v>91806</v>
+        <v>92684</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546564</v>
+        <v>546378</v>
       </c>
       <c r="R22" t="n">
-        <v>6690571</v>
+        <v>6691073</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2700,6 +2695,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128260976</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128258306</v>
       </c>
       <c r="B3" t="n">
-        <v>92639</v>
+        <v>92731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128259345</v>
       </c>
       <c r="B4" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128258256</v>
       </c>
       <c r="B5" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128260190</v>
       </c>
       <c r="B6" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128258240</v>
       </c>
       <c r="B7" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128258585</v>
       </c>
       <c r="B8" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128259599</v>
       </c>
       <c r="B9" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128260598</v>
       </c>
       <c r="B10" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>128259655</v>
       </c>
       <c r="B11" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128258089</v>
       </c>
       <c r="B12" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128258198</v>
+        <v>128260994</v>
       </c>
       <c r="B13" t="n">
-        <v>92057</v>
+        <v>92744</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>788</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546459</v>
+        <v>546356</v>
       </c>
       <c r="R13" t="n">
-        <v>6690988</v>
+        <v>6691087</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128260994</v>
+        <v>128258198</v>
       </c>
       <c r="B14" t="n">
-        <v>92652</v>
+        <v>92149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>788</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546356</v>
+        <v>546459</v>
       </c>
       <c r="R14" t="n">
-        <v>6691087</v>
+        <v>6690988</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1948,7 +1948,7 @@
         <v>128259095</v>
       </c>
       <c r="B15" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128258763</v>
+        <v>128259373</v>
       </c>
       <c r="B16" t="n">
-        <v>92057</v>
+        <v>88709</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>4405</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546506</v>
+        <v>546514</v>
       </c>
       <c r="R16" t="n">
-        <v>6690788</v>
+        <v>6690659</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128259373</v>
+        <v>128258763</v>
       </c>
       <c r="B17" t="n">
-        <v>88617</v>
+        <v>92149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4405</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546514</v>
+        <v>546506</v>
       </c>
       <c r="R17" t="n">
-        <v>6690659</v>
+        <v>6690788</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2239,7 +2239,7 @@
         <v>128259683</v>
       </c>
       <c r="B18" t="n">
-        <v>91656</v>
+        <v>91748</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>128259428</v>
       </c>
       <c r="B19" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128257918</v>
       </c>
       <c r="B20" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128259676</v>
       </c>
       <c r="B21" t="n">
-        <v>91814</v>
+        <v>91906</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128257989</v>
       </c>
       <c r="B22" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128260976</v>
+        <v>128259345</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>92776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546464</v>
+        <v>546505</v>
       </c>
       <c r="R2" t="n">
-        <v>6690810</v>
+        <v>6690671</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -878,45 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128259345</v>
+        <v>128260976</v>
       </c>
       <c r="B4" t="n">
-        <v>92776</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546505</v>
+        <v>546464</v>
       </c>
       <c r="R4" t="n">
-        <v>6690671</v>
+        <v>6690810</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128259373</v>
+        <v>128258763</v>
       </c>
       <c r="B16" t="n">
-        <v>88709</v>
+        <v>92149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4405</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546514</v>
+        <v>546506</v>
       </c>
       <c r="R16" t="n">
-        <v>6690659</v>
+        <v>6690788</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128258763</v>
+        <v>128259373</v>
       </c>
       <c r="B17" t="n">
-        <v>92149</v>
+        <v>88709</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>4405</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546506</v>
+        <v>546514</v>
       </c>
       <c r="R17" t="n">
-        <v>6690788</v>
+        <v>6690659</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2527,45 +2527,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128259676</v>
+        <v>128257989</v>
       </c>
       <c r="B21" t="n">
-        <v>91906</v>
+        <v>92776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546564</v>
+        <v>546378</v>
       </c>
       <c r="R21" t="n">
-        <v>6690571</v>
+        <v>6691073</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2598,6 +2598,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2624,45 +2629,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128257989</v>
+        <v>128259676</v>
       </c>
       <c r="B22" t="n">
-        <v>92776</v>
+        <v>91906</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546378</v>
+        <v>546564</v>
       </c>
       <c r="R22" t="n">
-        <v>6691073</v>
+        <v>6690571</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2695,11 +2700,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128260994</v>
+        <v>128258198</v>
       </c>
       <c r="B13" t="n">
-        <v>92744</v>
+        <v>92149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>788</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546356</v>
+        <v>546459</v>
       </c>
       <c r="R13" t="n">
-        <v>6691087</v>
+        <v>6690988</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128258198</v>
+        <v>128260994</v>
       </c>
       <c r="B14" t="n">
-        <v>92149</v>
+        <v>92744</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>788</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546459</v>
+        <v>546356</v>
       </c>
       <c r="R14" t="n">
-        <v>6690988</v>
+        <v>6691087</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128258763</v>
+        <v>128259373</v>
       </c>
       <c r="B16" t="n">
-        <v>92149</v>
+        <v>88709</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>4405</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546506</v>
+        <v>546514</v>
       </c>
       <c r="R16" t="n">
-        <v>6690788</v>
+        <v>6690659</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128259373</v>
+        <v>128258763</v>
       </c>
       <c r="B17" t="n">
-        <v>88709</v>
+        <v>92149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4405</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546514</v>
+        <v>546506</v>
       </c>
       <c r="R17" t="n">
-        <v>6690659</v>
+        <v>6690788</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128259345</v>
+        <v>128260976</v>
       </c>
       <c r="B2" t="n">
-        <v>92776</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546505</v>
+        <v>546464</v>
       </c>
       <c r="R2" t="n">
-        <v>6690671</v>
+        <v>6690810</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -775,7 +775,7 @@
         <v>128258306</v>
       </c>
       <c r="B3" t="n">
-        <v>92731</v>
+        <v>92743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,45 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128260976</v>
+        <v>128259345</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>92788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546464</v>
+        <v>546505</v>
       </c>
       <c r="R4" t="n">
-        <v>6690810</v>
+        <v>6690671</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +978,7 @@
         <v>128258256</v>
       </c>
       <c r="B5" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128260190</v>
       </c>
       <c r="B6" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128258240</v>
       </c>
       <c r="B7" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128258585</v>
       </c>
       <c r="B8" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128259599</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128260598</v>
       </c>
       <c r="B10" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>128259655</v>
       </c>
       <c r="B11" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128258089</v>
       </c>
       <c r="B12" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128258198</v>
       </c>
       <c r="B13" t="n">
-        <v>92149</v>
+        <v>92161</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>128260994</v>
       </c>
       <c r="B14" t="n">
-        <v>92744</v>
+        <v>92756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>128259095</v>
       </c>
       <c r="B15" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128259373</v>
+        <v>128258763</v>
       </c>
       <c r="B16" t="n">
-        <v>88709</v>
+        <v>92161</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4405</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546514</v>
+        <v>546506</v>
       </c>
       <c r="R16" t="n">
-        <v>6690659</v>
+        <v>6690788</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128258763</v>
+        <v>128259373</v>
       </c>
       <c r="B17" t="n">
-        <v>92149</v>
+        <v>88721</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>4405</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546506</v>
+        <v>546514</v>
       </c>
       <c r="R17" t="n">
-        <v>6690788</v>
+        <v>6690659</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2239,7 +2239,7 @@
         <v>128259683</v>
       </c>
       <c r="B18" t="n">
-        <v>91748</v>
+        <v>91760</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>128259428</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128257918</v>
       </c>
       <c r="B20" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,45 +2527,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128257989</v>
+        <v>128259676</v>
       </c>
       <c r="B21" t="n">
-        <v>92776</v>
+        <v>91918</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546378</v>
+        <v>546564</v>
       </c>
       <c r="R21" t="n">
-        <v>6691073</v>
+        <v>6690571</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2598,11 +2598,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2629,45 +2624,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128259676</v>
+        <v>128257989</v>
       </c>
       <c r="B22" t="n">
-        <v>91906</v>
+        <v>92788</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546564</v>
+        <v>546378</v>
       </c>
       <c r="R22" t="n">
-        <v>6690571</v>
+        <v>6691073</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2700,6 +2695,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128258198</v>
+        <v>128260994</v>
       </c>
       <c r="B13" t="n">
-        <v>92161</v>
+        <v>92756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>788</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546459</v>
+        <v>546356</v>
       </c>
       <c r="R13" t="n">
-        <v>6690988</v>
+        <v>6691087</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128260994</v>
+        <v>128258198</v>
       </c>
       <c r="B14" t="n">
-        <v>92756</v>
+        <v>92161</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>788</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546356</v>
+        <v>546459</v>
       </c>
       <c r="R14" t="n">
-        <v>6691087</v>
+        <v>6690988</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128260976</v>
+        <v>128259345</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>92790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546464</v>
+        <v>546505</v>
       </c>
       <c r="R2" t="n">
-        <v>6690810</v>
+        <v>6690671</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128258306</v>
+        <v>128260976</v>
       </c>
       <c r="B3" t="n">
-        <v>92743</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,43 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>150</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546466</v>
+        <v>546464</v>
       </c>
       <c r="R3" t="n">
-        <v>6690978</v>
+        <v>6690810</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -878,45 +869,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128259345</v>
+        <v>128258306</v>
       </c>
       <c r="B4" t="n">
-        <v>92788</v>
+        <v>92745</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546505</v>
+        <v>546466</v>
       </c>
       <c r="R4" t="n">
-        <v>6690671</v>
+        <v>6690978</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +978,7 @@
         <v>128258256</v>
       </c>
       <c r="B5" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128260190</v>
       </c>
       <c r="B6" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128258240</v>
       </c>
       <c r="B7" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128258585</v>
       </c>
       <c r="B8" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128259599</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128260598</v>
       </c>
       <c r="B10" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>128259655</v>
       </c>
       <c r="B11" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128258089</v>
       </c>
       <c r="B12" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128260994</v>
       </c>
       <c r="B13" t="n">
-        <v>92756</v>
+        <v>92758</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>128258198</v>
       </c>
       <c r="B14" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>128259095</v>
       </c>
       <c r="B15" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>128258763</v>
       </c>
       <c r="B16" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>128259373</v>
       </c>
       <c r="B17" t="n">
-        <v>88721</v>
+        <v>88723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>128259683</v>
       </c>
       <c r="B18" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>128259428</v>
       </c>
       <c r="B19" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128257918</v>
       </c>
       <c r="B20" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128259676</v>
       </c>
       <c r="B21" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128257989</v>
       </c>
       <c r="B22" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128259345</v>
+        <v>128258306</v>
       </c>
       <c r="B2" t="n">
-        <v>92790</v>
+        <v>92745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546505</v>
+        <v>546466</v>
       </c>
       <c r="R2" t="n">
-        <v>6690671</v>
+        <v>6690978</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,45 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128260976</v>
+        <v>128259345</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>92790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546464</v>
+        <v>546505</v>
       </c>
       <c r="R3" t="n">
-        <v>6690810</v>
+        <v>6690671</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128258306</v>
+        <v>128260976</v>
       </c>
       <c r="B4" t="n">
-        <v>92745</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,43 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>150</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546466</v>
+        <v>546464</v>
       </c>
       <c r="R4" t="n">
-        <v>6690978</v>
+        <v>6690810</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1366,7 +1366,7 @@
         <v>128259599</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,45 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128260598</v>
+        <v>128259655</v>
       </c>
       <c r="B10" t="n">
-        <v>92401</v>
+        <v>98591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pundberget, Pundberget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546520</v>
+        <v>546552</v>
       </c>
       <c r="R10" t="n">
-        <v>6690564</v>
+        <v>6690578</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1557,45 +1557,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128259655</v>
+        <v>128260598</v>
       </c>
       <c r="B11" t="n">
-        <v>98588</v>
+        <v>92401</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Pundberget, Pundberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546552</v>
+        <v>546520</v>
       </c>
       <c r="R11" t="n">
-        <v>6690578</v>
+        <v>6690564</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1948,7 +1948,7 @@
         <v>128259095</v>
       </c>
       <c r="B15" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>128259428</v>
       </c>
       <c r="B19" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128258306</v>
+        <v>128260976</v>
       </c>
       <c r="B2" t="n">
-        <v>92745</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>150</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546466</v>
+        <v>546464</v>
       </c>
       <c r="R2" t="n">
-        <v>6690978</v>
+        <v>6690810</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128260976</v>
+        <v>128258306</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>92745</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,34 +880,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546464</v>
+        <v>546466</v>
       </c>
       <c r="R4" t="n">
-        <v>6690810</v>
+        <v>6690978</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1460,45 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128259655</v>
+        <v>128260598</v>
       </c>
       <c r="B10" t="n">
-        <v>98591</v>
+        <v>92401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Pundberget, Pundberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546552</v>
+        <v>546520</v>
       </c>
       <c r="R10" t="n">
-        <v>6690578</v>
+        <v>6690564</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1557,45 +1557,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128260598</v>
+        <v>128259655</v>
       </c>
       <c r="B11" t="n">
-        <v>92401</v>
+        <v>98591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pundberget, Pundberget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546520</v>
+        <v>546552</v>
       </c>
       <c r="R11" t="n">
-        <v>6690564</v>
+        <v>6690578</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128260976</v>
+        <v>128258306</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>92746</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546464</v>
+        <v>546466</v>
       </c>
       <c r="R2" t="n">
-        <v>6690810</v>
+        <v>6690978</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -775,7 +784,7 @@
         <v>128259345</v>
       </c>
       <c r="B3" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128258306</v>
+        <v>128260976</v>
       </c>
       <c r="B4" t="n">
-        <v>92745</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,43 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>150</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546466</v>
+        <v>546464</v>
       </c>
       <c r="R4" t="n">
-        <v>6690978</v>
+        <v>6690810</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +978,7 @@
         <v>128258256</v>
       </c>
       <c r="B5" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128260190</v>
       </c>
       <c r="B6" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128258240</v>
       </c>
       <c r="B7" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128258585</v>
       </c>
       <c r="B8" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128259599</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,45 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128260598</v>
+        <v>128259655</v>
       </c>
       <c r="B10" t="n">
-        <v>92401</v>
+        <v>98592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pundberget, Pundberget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546520</v>
+        <v>546552</v>
       </c>
       <c r="R10" t="n">
-        <v>6690564</v>
+        <v>6690578</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1557,45 +1557,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128259655</v>
+        <v>128260598</v>
       </c>
       <c r="B11" t="n">
-        <v>98591</v>
+        <v>92402</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Pundberget, Pundberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546552</v>
+        <v>546520</v>
       </c>
       <c r="R11" t="n">
-        <v>6690578</v>
+        <v>6690564</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1657,7 +1657,7 @@
         <v>128258089</v>
       </c>
       <c r="B12" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128260994</v>
       </c>
       <c r="B13" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>128258198</v>
       </c>
       <c r="B14" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>128259095</v>
       </c>
       <c r="B15" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>128258763</v>
       </c>
       <c r="B16" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>128259683</v>
       </c>
       <c r="B18" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>128259428</v>
       </c>
       <c r="B19" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128257918</v>
       </c>
       <c r="B20" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,45 +2527,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128259676</v>
+        <v>128257989</v>
       </c>
       <c r="B21" t="n">
-        <v>91920</v>
+        <v>92791</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546564</v>
+        <v>546378</v>
       </c>
       <c r="R21" t="n">
-        <v>6690571</v>
+        <v>6691073</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2598,6 +2598,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2624,45 +2629,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128257989</v>
+        <v>128259676</v>
       </c>
       <c r="B22" t="n">
-        <v>92790</v>
+        <v>91921</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546378</v>
+        <v>546564</v>
       </c>
       <c r="R22" t="n">
-        <v>6691073</v>
+        <v>6690571</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2695,11 +2700,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -1460,45 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128259655</v>
+        <v>128260598</v>
       </c>
       <c r="B10" t="n">
-        <v>98592</v>
+        <v>92402</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Pundberget, Pundberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546552</v>
+        <v>546520</v>
       </c>
       <c r="R10" t="n">
-        <v>6690578</v>
+        <v>6690564</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1557,45 +1557,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128260598</v>
+        <v>128259655</v>
       </c>
       <c r="B11" t="n">
-        <v>92402</v>
+        <v>98592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pundberget, Pundberget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546520</v>
+        <v>546552</v>
       </c>
       <c r="R11" t="n">
-        <v>6690564</v>
+        <v>6690578</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128258306</v>
+        <v>128259345</v>
       </c>
       <c r="B2" t="n">
-        <v>92746</v>
+        <v>92818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546466</v>
+        <v>546505</v>
       </c>
       <c r="R2" t="n">
-        <v>6690978</v>
+        <v>6690671</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,45 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128259345</v>
+        <v>128258306</v>
       </c>
       <c r="B3" t="n">
-        <v>92791</v>
+        <v>92773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546505</v>
+        <v>546466</v>
       </c>
       <c r="R3" t="n">
-        <v>6690671</v>
+        <v>6690978</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,7 +881,7 @@
         <v>128260976</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128258256</v>
       </c>
       <c r="B5" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128260190</v>
       </c>
       <c r="B6" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128258240</v>
       </c>
       <c r="B7" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128258585</v>
       </c>
       <c r="B8" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128259599</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,45 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128260598</v>
+        <v>128259655</v>
       </c>
       <c r="B10" t="n">
-        <v>92402</v>
+        <v>98619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pundberget, Pundberget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546520</v>
+        <v>546552</v>
       </c>
       <c r="R10" t="n">
-        <v>6690564</v>
+        <v>6690578</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1557,45 +1557,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128259655</v>
+        <v>128260598</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>92429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Pundberget, Pundberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546552</v>
+        <v>546520</v>
       </c>
       <c r="R11" t="n">
-        <v>6690578</v>
+        <v>6690564</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1657,7 +1657,7 @@
         <v>128258089</v>
       </c>
       <c r="B12" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128260994</v>
+        <v>128258198</v>
       </c>
       <c r="B13" t="n">
-        <v>92759</v>
+        <v>92191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>788</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546356</v>
+        <v>546459</v>
       </c>
       <c r="R13" t="n">
-        <v>6691087</v>
+        <v>6690988</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128258198</v>
+        <v>128260994</v>
       </c>
       <c r="B14" t="n">
-        <v>92164</v>
+        <v>92786</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>788</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546459</v>
+        <v>546356</v>
       </c>
       <c r="R14" t="n">
-        <v>6690988</v>
+        <v>6691087</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1948,7 +1948,7 @@
         <v>128259095</v>
       </c>
       <c r="B15" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128258763</v>
+        <v>128259373</v>
       </c>
       <c r="B16" t="n">
-        <v>92164</v>
+        <v>88750</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>4405</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546506</v>
+        <v>546514</v>
       </c>
       <c r="R16" t="n">
-        <v>6690788</v>
+        <v>6690659</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128259373</v>
+        <v>128258763</v>
       </c>
       <c r="B17" t="n">
-        <v>88723</v>
+        <v>92191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4405</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546514</v>
+        <v>546506</v>
       </c>
       <c r="R17" t="n">
-        <v>6690659</v>
+        <v>6690788</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2239,7 +2239,7 @@
         <v>128259683</v>
       </c>
       <c r="B18" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>128259428</v>
       </c>
       <c r="B19" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128257918</v>
       </c>
       <c r="B20" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,45 +2527,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128257989</v>
+        <v>128259676</v>
       </c>
       <c r="B21" t="n">
-        <v>92791</v>
+        <v>91948</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546378</v>
+        <v>546564</v>
       </c>
       <c r="R21" t="n">
-        <v>6691073</v>
+        <v>6690571</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2598,11 +2598,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2629,45 +2624,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128259676</v>
+        <v>128257989</v>
       </c>
       <c r="B22" t="n">
-        <v>91921</v>
+        <v>92818</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546564</v>
+        <v>546378</v>
       </c>
       <c r="R22" t="n">
-        <v>6690571</v>
+        <v>6691073</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2700,6 +2695,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128259345</v>
+        <v>128258306</v>
       </c>
       <c r="B2" t="n">
-        <v>92818</v>
+        <v>92773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546505</v>
+        <v>546466</v>
       </c>
       <c r="R2" t="n">
-        <v>6690671</v>
+        <v>6690978</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,54 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128258306</v>
+        <v>128259345</v>
       </c>
       <c r="B3" t="n">
-        <v>92773</v>
+        <v>92818</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546466</v>
+        <v>546505</v>
       </c>
       <c r="R3" t="n">
-        <v>6690978</v>
+        <v>6690671</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -1460,45 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128259655</v>
+        <v>128260598</v>
       </c>
       <c r="B10" t="n">
-        <v>98619</v>
+        <v>92429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Pundberget, Pundberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546552</v>
+        <v>546520</v>
       </c>
       <c r="R10" t="n">
-        <v>6690578</v>
+        <v>6690564</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1557,45 +1557,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128260598</v>
+        <v>128259655</v>
       </c>
       <c r="B11" t="n">
-        <v>92429</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Pundberget, Pundberget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546520</v>
+        <v>546552</v>
       </c>
       <c r="R11" t="n">
-        <v>6690564</v>
+        <v>6690578</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128259373</v>
+        <v>128258763</v>
       </c>
       <c r="B16" t="n">
-        <v>88750</v>
+        <v>92191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4405</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546514</v>
+        <v>546506</v>
       </c>
       <c r="R16" t="n">
-        <v>6690659</v>
+        <v>6690788</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128258763</v>
+        <v>128259373</v>
       </c>
       <c r="B17" t="n">
-        <v>92191</v>
+        <v>88750</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>4405</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546506</v>
+        <v>546514</v>
       </c>
       <c r="R17" t="n">
-        <v>6690788</v>
+        <v>6690659</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2527,45 +2527,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128259676</v>
+        <v>128257989</v>
       </c>
       <c r="B21" t="n">
-        <v>91948</v>
+        <v>92818</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546564</v>
+        <v>546378</v>
       </c>
       <c r="R21" t="n">
-        <v>6690571</v>
+        <v>6691073</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2598,6 +2598,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2624,45 +2629,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128257989</v>
+        <v>128259676</v>
       </c>
       <c r="B22" t="n">
-        <v>92818</v>
+        <v>91948</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546378</v>
+        <v>546564</v>
       </c>
       <c r="R22" t="n">
-        <v>6691073</v>
+        <v>6690571</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2695,11 +2700,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128258306</v>
       </c>
       <c r="B2" t="n">
-        <v>92783</v>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128259345</v>
+        <v>128259683</v>
       </c>
       <c r="B3" t="n">
-        <v>92830</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546505</v>
+        <v>546568</v>
       </c>
       <c r="R3" t="n">
-        <v>6690671</v>
+        <v>6690567</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128260976</v>
+        <v>128260994</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>93199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546464</v>
+        <v>546356</v>
       </c>
       <c r="R4" t="n">
-        <v>6690810</v>
+        <v>6691087</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,45 +975,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128258256</v>
+        <v>128260190</v>
       </c>
       <c r="B5" t="n">
-        <v>92439</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Pundberget, Pundberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546470</v>
+        <v>546577</v>
       </c>
       <c r="R5" t="n">
-        <v>6690992</v>
+        <v>6690389</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128260190</v>
+        <v>128259676</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,34 +1083,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pundberget, Pundberget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546577</v>
+        <v>546564</v>
       </c>
       <c r="R6" t="n">
-        <v>6690389</v>
+        <v>6690571</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128258240</v>
+        <v>128258198</v>
       </c>
       <c r="B7" t="n">
-        <v>92830</v>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546464</v>
+        <v>546459</v>
       </c>
       <c r="R7" t="n">
-        <v>6690996</v>
+        <v>6690988</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1266,45 +1266,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128258585</v>
+        <v>128258763</v>
       </c>
       <c r="B8" t="n">
-        <v>92812</v>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4368</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546473</v>
+        <v>546506</v>
       </c>
       <c r="R8" t="n">
-        <v>6690951</v>
+        <v>6690788</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1363,45 +1363,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128259599</v>
+        <v>128258089</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>93215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546511</v>
+        <v>546420</v>
       </c>
       <c r="R9" t="n">
-        <v>6690641</v>
+        <v>6691048</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1460,45 +1460,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128260598</v>
+        <v>128258585</v>
       </c>
       <c r="B10" t="n">
-        <v>92439</v>
+        <v>93215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pundberget, Pundberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546520</v>
+        <v>546473</v>
       </c>
       <c r="R10" t="n">
-        <v>6690564</v>
+        <v>6690951</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1557,45 +1557,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128259655</v>
+        <v>128260988</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>93215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546552</v>
+        <v>546330</v>
       </c>
       <c r="R11" t="n">
-        <v>6690578</v>
+        <v>6691091</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1654,45 +1654,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128258089</v>
+        <v>128259373</v>
       </c>
       <c r="B12" t="n">
-        <v>92812</v>
+        <v>89143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4368</v>
+        <v>4405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546420</v>
+        <v>546514</v>
       </c>
       <c r="R12" t="n">
-        <v>6691048</v>
+        <v>6690659</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128260994</v>
+        <v>128257918</v>
       </c>
       <c r="B13" t="n">
-        <v>92796</v>
+        <v>92869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546356</v>
+        <v>546375</v>
       </c>
       <c r="R13" t="n">
-        <v>6691087</v>
+        <v>6691107</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128258198</v>
+        <v>128258256</v>
       </c>
       <c r="B14" t="n">
-        <v>92201</v>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546459</v>
+        <v>546470</v>
       </c>
       <c r="R14" t="n">
-        <v>6690988</v>
+        <v>6690992</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1945,45 +1945,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128259095</v>
+        <v>128260598</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>92869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Pundberget, Pundberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546521</v>
+        <v>546520</v>
       </c>
       <c r="R15" t="n">
-        <v>6690766</v>
+        <v>6690564</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2042,45 +2042,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128258763</v>
+        <v>128257989</v>
       </c>
       <c r="B16" t="n">
-        <v>92201</v>
+        <v>93233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546506</v>
+        <v>546378</v>
       </c>
       <c r="R16" t="n">
-        <v>6690788</v>
+        <v>6691073</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2113,6 +2113,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2139,45 +2144,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128259373</v>
+        <v>128258240</v>
       </c>
       <c r="B17" t="n">
-        <v>88755</v>
+        <v>93233</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
+          <t>Traskänget, Traskänget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546514</v>
+        <v>546464</v>
       </c>
       <c r="R17" t="n">
-        <v>6690659</v>
+        <v>6690996</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2236,10 +2241,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128259683</v>
+        <v>128259345</v>
       </c>
       <c r="B18" t="n">
-        <v>91800</v>
+        <v>93233</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2252,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546568</v>
+        <v>546505</v>
       </c>
       <c r="R18" t="n">
-        <v>6690567</v>
+        <v>6690671</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2333,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128259428</v>
+        <v>128259095</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2368,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546514</v>
+        <v>546521</v>
       </c>
       <c r="R19" t="n">
-        <v>6690665</v>
+        <v>6690766</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2430,45 +2435,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128257918</v>
+        <v>128259428</v>
       </c>
       <c r="B20" t="n">
-        <v>92439</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546375</v>
+        <v>546514</v>
       </c>
       <c r="R20" t="n">
-        <v>6691107</v>
+        <v>6690665</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2527,45 +2532,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128257989</v>
+        <v>128259599</v>
       </c>
       <c r="B21" t="n">
-        <v>92830</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Traskänget, Traskänget, Dlr</t>
+          <t>Fällkolningsberget, Fällkolningsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546378</v>
+        <v>546511</v>
       </c>
       <c r="R21" t="n">
-        <v>6691073</v>
+        <v>6690641</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2598,11 +2603,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Stort mycel.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2629,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128259676</v>
+        <v>128259655</v>
       </c>
       <c r="B22" t="n">
-        <v>91958</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546564</v>
+        <v>546552</v>
       </c>
       <c r="R22" t="n">
-        <v>6690571</v>
+        <v>6690578</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2723,6 +2723,103 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128260818</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Traskänget, Traskänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>546464</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6690810</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54120-2024 artfynd.xlsx
+++ b/artfynd/A 54120-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128258306</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128259683</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260994</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260190</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128259676</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128258198</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128258763</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128258089</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128258585</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260988</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128259373</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,6 +1905,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128257918</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,6 +2007,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128258256</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2039,6 +2109,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260598</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2141,6 +2216,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128257989</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2238,6 +2318,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128258240</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2335,6 +2420,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128259345</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2432,6 +2522,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128259095</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2529,6 +2624,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128259428</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2626,6 +2726,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128259599</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2723,6 +2828,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128259655</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2820,8 +2930,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260818</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>